--- a/Luban/Config/Datas/Levels/L14/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L14/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L14 W1/25; N=44; EHP=267.168000; normal:17x22,normal:18x22</t>
+          <t>L14 W1/25; N=44; EHP=630.606266; normal:17x22,normal:18x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L14 W2/25; N=50; EHP=317.899560; normal:17x25,normal:18x25</t>
+          <t>L14 W2/25; N=50; EHP=750.349796; normal:17x25,normal:18x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3624136,3624673,3624019,3624136,3624673,3624019,3624136,3624673,3624091,3624136,3624673,3624099,3624136,3624673,3624099,3624136,3624673,3624107,3624136,3624673,3624115,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624136,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144</t>
+          <t>3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624673,3624136,3624136,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624144,3624136,3624136,3624136,3624136,3624136,3624136,3624136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L14 W3/25; N=56; EHP=393.893069; air:2x2,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x17,normal:18x17,swarm:84x15</t>
+          <t>L14 W3/25; N=56; EHP=1006.040316; normal:17x24,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3626136,3626673,3626019,3626136,3626673,3626019,3626136,3626673,3626091,3626136,3626673,3626099,3626136,3626673,3626107,3626136,3626673,3626107,3626136,3626673,3626115,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626136,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144</t>
+          <t>3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626673,3626136,3626136,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626144,3626136,3626136,3626136,3626136,3626136,3626136,3626136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L14 W4/25; N=62; EHP=502.165330; air:2x2,air:11x1,air:12x1,air:13x2,air:14x1,normal:17x19,normal:18x19,swarm:84x17</t>
+          <t>L14 W4/25; N=62; EHP=1272.698936; normal:17x26,normal:18x19,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3628136,3628673,3628019,3628668,3628136,3628673,3628091,3628668,3628136,3628673,3628091,3628668,3628136,3628673,3628099,3628868,3628136,3628673,3628107,3628868,3628136,3628673,3628107,3628868,3628136,3628673,3628115,3628988,3628136,3628673,3628115,3628988,3628136,3628673,3628988,3628136,3628673,3628988,3628136,3628673,3628136,3628673,3628136,3628673,3628136,3628673,3628136,3628673,3628136,3628673,3628144,3628673,3628144,3628673,3628144,3628673,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144</t>
+          <t>3628136,3628019,3628019,3628668,3628136,3628091,3628091,3628668,3628136,3628091,3628091,3628668,3628136,3628099,3628099,3628868,3628136,3628107,3628107,3628868,3628136,3628107,3628107,3628868,3628136,3628115,3628115,3628988,3628136,3628115,3628115,3628988,3628136,3628673,3628988,3628136,3628673,3628988,3628136,3628673,3628136,3628673,3628136,3628673,3628136,3628673,3628136,3628673,3628136,3628673,3628144,3628673,3628144,3628673,3628144,3628673,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144,3628144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L14 W5/25; N=68; EHP=948.610393; air:2x1,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x16,normal:18x15,medium:83x3,swarm:84x19,medium:108x3,medium:123x4</t>
+          <t>L14 W5/25; N=68; EHP=2267.049195; air:2x2,air:11x4,air:12x2,air:13x4,air:14x4,medium:83x3,medium:108x3,medium:123x4,normal:17x16,normal:18x15,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3630136,3630673,3630242,3630019,3630668,3630136,3630673,3630242,3630019,3630668,3630136,3630673,3630466,3630091,3630668,3630136,3630673,3630466,3630091,3630668,3630136,3630673,3630514,3630099,3630868,3630136,3630673,3630514,3630099,3630868,3630136,3630673,3630786,3630107,3630868,3630136,3630673,3630786,3630115,3630868,3630136,3630673,3630115,3630988,3630136,3630673,3630988,3630136,3630673,3630988,3630136,3630673,3630136,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630144,3630144,3630144,3630144,3630144</t>
+          <t>3630136,3630019,3630242,3630019,3630668,3630136,3630019,3630242,3630019,3630668,3630136,3630091,3630466,3630091,3630668,3630136,3630091,3630466,3630091,3630668,3630136,3630099,3630514,3630099,3630868,3630136,3630099,3630514,3630099,3630868,3630136,3630107,3630786,3630107,3630868,3630136,3630115,3630786,3630115,3630868,3630136,3630115,3630115,3630988,3630136,3630673,3630988,3630136,3630673,3630988,3630136,3630673,3630136,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630673,3630144,3630144,3630144,3630144,3630144,3630144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L14 W6/25; N=74; EHP=968.000000; air:2x2,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x13,normal:18x13,fast:30x2,fast:58x2,fast:64x2,medium:83x4,swarm:84x20,fast:98x2,medium:108x4,medium:123x3</t>
+          <t>L14 W6/25; N=74; EHP=2314.802754; air:2x4,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x2,medium:83x4,medium:108x4,medium:123x3,normal:17x13,normal:18x13,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3632136,3632673,3632242,3632019,3632668,3632136,3632673,3632242,3632019,3632668,3632136,3632673,3632466,3632091,3632668,3632136,3632673,3632466,3632091,3632668,3632136,3632673,3632514,3632099,3632868,3632136,3632673,3632514,3632099,3632868,3632136,3632673,3632786,3632107,3632868,3632136,3632673,3632786,3632107,3632868,3632136,3632673,3632786,3632115,3632988,3632136,3632673,3632115,3632988,3632136,3632673,3632988,3632136,3632673,3632988,3632136,3632673,3632136,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632144,3632144,3632144,3632144</t>
+          <t>3632136,3632019,3632242,3632019,3632668,3632136,3632019,3632242,3632019,3632668,3632136,3632091,3632466,3632091,3632668,3632136,3632091,3632466,3632091,3632668,3632136,3632099,3632514,3632099,3632868,3632136,3632099,3632514,3632099,3632868,3632136,3632107,3632786,3632107,3632868,3632136,3632107,3632786,3632107,3632868,3632136,3632115,3632786,3632115,3632988,3632136,3632115,3632115,3632988,3632136,3632673,3632988,3632136,3632673,3632988,3632136,3632673,3632136,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632673,3632144,3632144,3632144,3632144,3632144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L14 W7/25; N=80; EHP=1092.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x13,fast:30x2,fast:58x2,fast:64x2,medium:83x4,swarm:84x22,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L14 W7/25; N=80; EHP=2612.388634; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x13,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3634136,3634673,3634242,3634019,3634668,3634136,3634673,3634242,3634019,3634668,3634136,3634673,3634466,3634091,3634668,3634136,3634673,3634466,3634091,3634668,3634136,3634673,3634466,3634099,3634868,3634136,3634673,3634514,3634099,3634868,3634136,3634673,3634514,3634107,3634868,3634136,3634673,3634514,3634107,3634868,3634136,3634673,3634786,3634115,3634988,3634136,3634673,3634786,3634115,3634988,3634136,3634673,3634988,3634136,3634673,3634988,3634136,3634673,3634136,3634673,3634136,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634144,3634144,3634144,3634144,3634144</t>
+          <t>3634136,3634019,3634242,3634019,3634668,3634136,3634019,3634242,3634019,3634668,3634136,3634091,3634466,3634091,3634668,3634136,3634091,3634466,3634091,3634668,3634136,3634099,3634466,3634099,3634868,3634136,3634099,3634514,3634099,3634868,3634136,3634107,3634514,3634107,3634868,3634136,3634107,3634514,3634107,3634868,3634136,3634115,3634786,3634115,3634988,3634136,3634115,3634786,3634115,3634988,3634136,3634673,3634988,3634136,3634673,3634988,3634136,3634673,3634136,3634673,3634136,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634673,3634144,3634144,3634144,3634144,3634144,3634144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L14 W8/25; N=86; EHP=1404.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x24,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L14 W8/25; N=86; EHP=3355.860085; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3636136,3636673,3636242,3636019,3636668,3636136,3636673,3636242,3636019,3636668,3636136,3636673,3636242,3636019,3636668,3636136,3636673,3636466,3636091,3636668,3636136,3636673,3636466,3636091,3636868,3636136,3636673,3636514,3636099,3636868,3636136,3636673,3636514,3636099,3636868,3636136,3636673,3636514,3636107,3636868,3636136,3636673,3636786,3636107,3636868,3636136,3636673,3636786,3636115,3636988,3636136,3636673,3636786,3636115,3636988,3636136,3636673,3636988,3636136,3636673,3636988,3636136,3636673,3636136,3636673,3636136,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636144,3636144,3636144,3636144,3636144,3636144</t>
+          <t>3636136,3636019,3636242,3636019,3636668,3636136,3636019,3636242,3636019,3636668,3636136,3636019,3636242,3636019,3636668,3636136,3636091,3636466,3636091,3636668,3636136,3636091,3636466,3636091,3636868,3636136,3636099,3636514,3636099,3636868,3636136,3636099,3636514,3636099,3636868,3636136,3636107,3636514,3636107,3636868,3636136,3636107,3636786,3636107,3636868,3636136,3636115,3636786,3636115,3636988,3636136,3636115,3636786,3636115,3636988,3636136,3636673,3636988,3636136,3636673,3636988,3636136,3636673,3636136,3636673,3636136,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636673,3636144,3636144,3636144,3636144,3636144,3636144,3636144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L14 W9/25; N=92; EHP=1793.000000; air:2x3,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x16,normal:18x16,fast:30x3,fast:58x2,fast:64x3,medium:83x4,swarm:84x25,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L14 W9/25; N=92; EHP=4287.077139; air:2x6,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x3,medium:83x4,medium:108x5,medium:123x4,normal:17x16,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3638136,3638673,3638242,3638019,3638668,3638136,3638673,3638242,3638019,3638668,3638136,3638673,3638242,3638091,3638668,3638136,3638673,3638466,3638091,3638668,3638136,3638673,3638466,3638091,3638668,3638136,3638673,3638466,3638099,3638868,3638136,3638673,3638514,3638099,3638868,3638136,3638673,3638514,3638107,3638868,3638136,3638673,3638786,3638107,3638868,3638136,3638673,3638786,3638107,3638988,3638136,3638673,3638786,3638115,3638988,3638136,3638673,3638115,3638988,3638136,3638673,3638988,3638136,3638673,3638988,3638136,3638673,3638136,3638673,3638136,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638144,3638144,3638144,3638144,3638144,3638144</t>
+          <t>3638136,3638019,3638242,3638019,3638668,3638136,3638019,3638242,3638019,3638668,3638136,3638091,3638242,3638091,3638668,3638136,3638091,3638466,3638091,3638668,3638136,3638091,3638466,3638091,3638668,3638136,3638099,3638466,3638099,3638868,3638136,3638099,3638514,3638099,3638868,3638136,3638107,3638514,3638107,3638868,3638136,3638107,3638786,3638107,3638868,3638136,3638107,3638786,3638107,3638988,3638136,3638115,3638786,3638115,3638988,3638136,3638115,3638115,3638988,3638136,3638673,3638988,3638136,3638673,3638988,3638136,3638673,3638136,3638673,3638136,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638673,3638144,3638144,3638144,3638144,3638144,3638144,3638144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L14 W10/25; N=98; EHP=3307.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x17,fast:30x3,fast:58x3,fast:64x2,medium:83x5,swarm:84x27,fast:98x3,medium:108x4,medium:123x5</t>
+          <t>L14 W10/25; N=98; EHP=7909.590939; air:2x4,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x2,fast:98x3,medium:83x5,medium:108x4,medium:123x5,normal:17x17,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3640136,3640673,3640242,3640019,3640668,3640253,3640136,3640673,3640242,3640019,3640668,3640325,3640136,3640673,3640242,3640091,3640668,3640541,3640136,3640673,3640466,3640091,3640668,3640565,3640136,3640673,3640466,3640091,3640668,3640645,3640136,3640673,3640466,3640099,3640868,3640645,3640136,3640673,3640514,3640099,3640868,3640693,3640136,3640673,3640514,3640107,3640868,3640693,3640136,3640673,3640514,3640107,3640868,3640709,3640136,3640673,3640786,3640115,3640868,3641021,3640136,3640673,3640786,3640115,3640988,3640136,3640673,3640786,3640115,3640988,3640136,3640673,3640988,3640144,3640673,3640988,3640144,3640673,3640988,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640673,3640673,3640673</t>
+          <t>3640136,3640019,3640242,3640019,3640668,3640253,3640136,3640019,3640242,3640019,3640668,3640325,3640136,3640091,3640242,3640091,3640668,3640541,3640136,3640091,3640466,3640091,3640668,3640565,3640136,3640091,3640466,3640091,3640668,3640645,3640136,3640099,3640466,3640099,3640868,3640645,3640136,3640099,3640514,3640099,3640868,3640693,3640136,3640107,3640514,3640107,3640868,3640693,3640136,3640107,3640514,3640107,3640868,3640709,3640136,3640115,3640786,3640115,3640868,3641021,3640136,3640115,3640786,3640115,3640988,3640136,3640115,3640786,3640115,3640988,3640136,3640673,3640988,3640144,3640673,3640988,3640144,3640673,3640988,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640144,3640673,3640673,3640673,3640673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L14 W11/25; N=104; EHP=3374.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x3,normal:17x13,normal:18x13,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x29,heavy:86x2,heavy:88x1,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L14 W11/25; N=104; EHP=8052.301242; air:2x4,air:11x6,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x5,medium:123x5,normal:17x13,normal:18x13,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3642136,3642673,3642242,3642019,3642668,3642253,3642136,3642673,3642242,3642019,3642668,3642253,3642136,3642673,3642242,3642019,3642668,3642325,3642136,3642673,3642466,3642091,3642668,3642325,3642136,3642673,3642466,3642091,3642668,3642541,3642136,3642673,3642466,3642099,3642868,3642565,3642136,3642673,3642466,3642099,3642868,3642645,3642136,3642673,3642514,3642099,3642868,3642693,3642136,3642673,3642514,3642107,3642868,3642693,3642136,3642673,3642514,3642107,3642868,3642709,3642136,3642673,3642786,3642115,3642868,3643021,3642136,3642673,3642786,3642115,3642988,3642136,3642673,3642786,3642115,3642988,3642144,3642673,3642988,3642144,3642673,3642988,3642144,3642673,3642988,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642673,3642673,3642673</t>
+          <t>3642136,3642019,3642242,3642019,3642668,3642253,3642136,3642019,3642242,3642019,3642668,3642253,3642136,3642019,3642242,3642019,3642668,3642325,3642136,3642091,3642466,3642091,3642668,3642325,3642136,3642091,3642466,3642091,3642668,3642541,3642136,3642099,3642466,3642099,3642868,3642565,3642136,3642099,3642466,3642099,3642868,3642645,3642136,3642099,3642514,3642099,3642868,3642693,3642136,3642107,3642514,3642107,3642868,3642693,3642136,3642107,3642514,3642107,3642868,3642709,3642136,3642115,3642786,3642115,3642868,3643021,3642136,3642115,3642786,3642115,3642988,3642136,3642115,3642786,3642115,3642988,3642144,3642673,3642988,3642144,3642673,3642988,3642144,3642673,3642988,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642144,3642673,3642673,3642673,3642673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L14 W12/25; N=110; EHP=3492.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x14,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x5,swarm:84x30,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x5,heavy:127x1</t>
+          <t>L14 W12/25; N=110; EHP=8335.629613; air:2x6,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x6,medium:123x5,normal:17x13,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3644136,3644673,3644242,3644019,3644668,3644253,3644136,3644673,3644242,3644019,3644668,3644253,3644136,3644673,3644242,3644019,3644668,3644325,3644136,3644673,3644466,3644091,3644668,3644325,3644136,3644673,3644466,3644091,3644668,3644541,3644136,3644673,3644466,3644091,3644668,3644565,3644136,3644673,3644514,3644099,3644868,3644645,3644136,3644673,3644514,3644099,3644868,3644693,3644136,3644673,3644514,3644099,3644868,3644709,3644136,3644673,3644514,3644107,3644868,3645021,3644136,3644673,3644786,3644107,3644868,3645021,3644136,3644673,3644786,3644107,3644988,3644136,3644673,3644786,3644115,3644988,3644136,3644673,3644115,3644988,3644136,3644673,3644988,3644144,3644673,3644988,3644144,3644673,3644988,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644673,3644673,3644673</t>
+          <t>3644136,3644019,3644242,3644019,3644668,3644253,3644136,3644019,3644242,3644019,3644668,3644253,3644136,3644019,3644242,3644019,3644668,3644325,3644136,3644091,3644466,3644091,3644668,3644325,3644136,3644091,3644466,3644091,3644668,3644541,3644136,3644091,3644466,3644091,3644668,3644565,3644136,3644099,3644514,3644099,3644868,3644645,3644136,3644099,3644514,3644099,3644868,3644693,3644136,3644099,3644514,3644099,3644868,3644709,3644136,3644107,3644514,3644107,3644868,3645021,3644136,3644107,3644786,3644107,3644868,3645021,3644136,3644107,3644786,3644107,3644988,3644136,3644115,3644786,3644115,3644988,3644136,3644115,3644115,3644988,3644136,3644673,3644988,3644144,3644673,3644988,3644144,3644673,3644988,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644144,3644673,3644673,3644673,3644673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L14 W13/25; N=116; EHP=4260.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x2,normal:17x15,normal:18x14,fast:30x3,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x32,heavy:86x1,heavy:88x1,fast:98x3,medium:108x5,medium:123x6,heavy:127x2</t>
+          <t>L14 W13/25; N=116; EHP=10172.096451; air:2x6,air:11x6,air:12x6,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x5,medium:123x6,normal:17x15,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3646136,3646673,3646242,3646019,3646668,3646253,3646136,3646673,3646242,3646019,3646668,3646325,3646136,3646673,3646242,3646019,3646668,3646325,3646136,3646673,3646242,3646091,3646668,3646541,3646136,3646673,3646466,3646091,3646668,3646541,3646136,3646673,3646466,3646091,3646668,3646565,3646136,3646673,3646466,3646099,3646868,3646565,3646136,3646673,3646514,3646099,3646868,3646645,3646136,3646673,3646514,3646099,3646868,3646693,3646136,3646673,3646514,3646107,3646868,3646709,3646136,3646673,3646786,3646107,3646868,3647021,3646136,3646673,3646786,3646107,3646868,3647021,3646136,3646673,3646786,3646115,3646988,3646136,3646673,3646786,3646115,3646988,3646144,3646673,3646115,3646988,3646144,3646673,3646988,3646144,3646673,3646988,3646144,3646673,3646988,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646673,3646673,3646673,3646673,3646673</t>
+          <t>3646136,3646019,3646242,3646019,3646668,3646253,3646136,3646019,3646242,3646019,3646668,3646325,3646136,3646019,3646242,3646019,3646668,3646325,3646136,3646091,3646242,3646091,3646668,3646541,3646136,3646091,3646466,3646091,3646668,3646541,3646136,3646091,3646466,3646091,3646668,3646565,3646136,3646099,3646466,3646099,3646868,3646565,3646136,3646099,3646514,3646099,3646868,3646645,3646136,3646099,3646514,3646099,3646868,3646693,3646136,3646107,3646514,3646107,3646868,3646709,3646136,3646107,3646786,3646107,3646868,3647021,3646136,3646107,3646786,3646107,3646868,3647021,3646136,3646115,3646786,3646115,3646988,3646136,3646115,3646786,3646115,3646988,3646144,3646115,3646115,3646988,3646144,3646673,3646988,3646144,3646673,3646988,3646144,3646673,3646988,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646144,3646673,3646673,3646673,3646673,3646673,3646673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L14 W14/25; N=122; EHP=5140.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x4,heavy:31x1,heavy:40x2,fast:58x3,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x34,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L14 W14/25; N=122; EHP=12275.702843; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3648136,3648673,3648242,3648019,3648668,3648253,3648542,3648136,3648673,3648242,3648019,3648668,3648325,3648136,3648673,3648242,3648019,3648668,3648541,3648136,3648673,3648466,3648091,3648668,3648541,3648136,3648673,3648466,3648091,3648668,3648565,3648136,3648673,3648466,3648091,3648668,3648565,3648136,3648673,3648466,3648099,3648868,3648645,3648136,3648673,3648514,3648099,3648868,3648693,3648136,3648673,3648514,3648099,3648868,3648709,3648136,3648673,3648514,3648107,3648868,3648709,3648136,3648673,3648514,3648107,3648868,3649021,3648136,3648673,3648786,3648107,3648868,3649021,3648136,3648673,3648786,3648115,3648868,3648136,3648673,3648786,3648115,3648988,3648136,3648673,3648786,3648115,3648988,3648136,3648673,3648988,3648144,3648673,3648988,3648144,3648673,3648988,3648144,3648673,3648988,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648673,3648673,3648673,3648673</t>
+          <t>3648136,3648019,3648242,3648019,3648668,3648253,3648542,3648136,3648019,3648242,3648019,3648668,3648325,3648136,3648019,3648242,3648019,3648668,3648541,3648136,3648091,3648466,3648091,3648668,3648541,3648136,3648091,3648466,3648091,3648668,3648565,3648136,3648091,3648466,3648091,3648668,3648565,3648136,3648099,3648466,3648099,3648868,3648645,3648136,3648099,3648514,3648099,3648868,3648693,3648136,3648099,3648514,3648099,3648868,3648709,3648136,3648107,3648514,3648107,3648868,3648709,3648136,3648107,3648514,3648107,3648868,3649021,3648136,3648107,3648786,3648107,3648868,3649021,3648136,3648115,3648786,3648115,3648868,3648136,3648115,3648786,3648115,3648988,3648136,3648115,3648786,3648115,3648988,3648136,3648673,3648988,3648144,3648673,3648988,3648144,3648673,3648988,3648144,3648673,3648988,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648144,3648673,3648673,3648673,3648673,3648673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L14 W15/25; N=128; EHP=8971.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x15,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x35,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L14 W15/25; N=128; EHP=21406.837080; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,elite:67x1,fast:30x3,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x7,medium:123x6,normal:17x16,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3650136,3650673,3650242,3650019,3650668,3650253,3650136,3650673,3650242,3650019,3650668,3650325,3650136,3650673,3650242,3650019,3650668,3650541,3650136,3650673,3650242,3650091,3650668,3650541,3650136,3650673,3650466,3650091,3650668,3650565,3650136,3650673,3650466,3650091,3650668,3650565,3650136,3650673,3650466,3650091,3650668,3650645,3650136,3650673,3650466,3650099,3650868,3650645,3650136,3650673,3650514,3650099,3650868,3650693,3650136,3650673,3650514,3650099,3650868,3650693,3650136,3650673,3650514,3650107,3650868,3650709,3650136,3650673,3650514,3650107,3650868,3650709,3650136,3650673,3650786,3650107,3650868,3651021,3650136,3650673,3650786,3650115,3650988,3650136,3650673,3650786,3650115,3650988,3650136,3650673,3650786,3650115,3650988,3650144,3650673,3650988,3650144,3650673,3650988,3650144,3650673,3650988,3650144,3650673,3650988,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650673,3650673,3650673,3650673,3650673</t>
+          <t>3650136,3650019,3650242,3650019,3650668,3650253,3650136,3650019,3650242,3650019,3650668,3650325,3650136,3650019,3650242,3650019,3650668,3650541,3650136,3650091,3650242,3650091,3650668,3650541,3650136,3650091,3650466,3650091,3650668,3650565,3650136,3650091,3650466,3650091,3650668,3650565,3650136,3650091,3650466,3650091,3650668,3650645,3650136,3650099,3650466,3650099,3650868,3650645,3650136,3650099,3650514,3650099,3650868,3650693,3650136,3650099,3650514,3650099,3650868,3650693,3650136,3650107,3650514,3650107,3650868,3650709,3650136,3650107,3650514,3650107,3650868,3650709,3650136,3650107,3650786,3650107,3650868,3651021,3650136,3650115,3650786,3650115,3650988,3650136,3650115,3650786,3650115,3650988,3650136,3650115,3650786,3650115,3650988,3650144,3650673,3650988,3650144,3650673,3650988,3650144,3650673,3650988,3650144,3650673,3650988,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650144,3650673,3650673,3650673,3650673,3650673,3650673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L14 W16/25; N=134; EHP=9151.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x37,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x1</t>
+          <t>L14 W16/25; N=134; EHP=21847.259610; air:2x6,air:11x8,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3652136,3652673,3652242,3652019,3652668,3652253,3652136,3652673,3652242,3652019,3652668,3652253,3652136,3652673,3652242,3652019,3652668,3652325,3652136,3652673,3652242,3652091,3652668,3652325,3652136,3652673,3652466,3652091,3652668,3652541,3652136,3652673,3652466,3652091,3652668,3652541,3652136,3652673,3652466,3652099,3652668,3652565,3652136,3652673,3652466,3652099,3652868,3652645,3652136,3652673,3652514,3652099,3652868,3652645,3652136,3652673,3652514,3652099,3652868,3652693,3652136,3652673,3652514,3652107,3652868,3652693,3652136,3652673,3652514,3652107,3652868,3652709,3652136,3652673,3652786,3652107,3652868,3652709,3652136,3652673,3652786,3652115,3652868,3653021,3652136,3652673,3652786,3652115,3652988,3652136,3652673,3652786,3652115,3652988,3652136,3652673,3652115,3652988,3652144,3652673,3652988,3652144,3652673,3652988,3652144,3652673,3652988,3652144,3652673,3652988,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652673,3652673,3652673,3652673,3652673,3652673</t>
+          <t>3652136,3652019,3652242,3652019,3652668,3652253,3652136,3652019,3652242,3652019,3652668,3652253,3652136,3652019,3652242,3652019,3652668,3652325,3652136,3652091,3652242,3652091,3652668,3652325,3652136,3652091,3652466,3652091,3652668,3652541,3652136,3652091,3652466,3652091,3652668,3652541,3652136,3652099,3652466,3652099,3652668,3652565,3652136,3652099,3652466,3652099,3652868,3652645,3652136,3652099,3652514,3652099,3652868,3652645,3652136,3652099,3652514,3652099,3652868,3652693,3652136,3652107,3652514,3652107,3652868,3652693,3652136,3652107,3652514,3652107,3652868,3652709,3652136,3652107,3652786,3652107,3652868,3652709,3652136,3652115,3652786,3652115,3652868,3653021,3652136,3652115,3652786,3652115,3652988,3652136,3652115,3652786,3652115,3652988,3652136,3652115,3652115,3652988,3652144,3652673,3652988,3652144,3652673,3652988,3652144,3652673,3652988,3652144,3652673,3652988,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652144,3652673,3652673,3652673,3652673,3652673,3652673,3652673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L14 W17/25; N=140; EHP=9335.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x17,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L14 W17/25; N=140; EHP=22290.118770; air:2x6,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x16,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3654136,3654673,3654242,3654019,3654668,3654253,3654136,3654673,3654242,3654019,3654668,3654253,3654136,3654673,3654242,3654019,3654668,3654325,3654136,3654673,3654242,3654019,3654668,3654325,3654136,3654673,3654242,3654091,3654668,3654541,3654136,3654673,3654466,3654091,3654668,3654565,3654136,3654673,3654466,3654091,3654668,3654645,3654136,3654673,3654466,3654099,3654868,3654645,3654136,3654673,3654466,3654099,3654868,3654693,3654136,3654673,3654514,3654099,3654868,3654693,3654136,3654673,3654514,3654099,3654868,3654709,3654136,3654673,3654514,3654107,3654868,3654709,3654136,3654673,3654514,3654107,3654868,3655021,3654136,3654673,3654786,3654107,3654868,3655021,3654136,3654673,3654786,3654107,3654988,3654136,3654673,3654786,3654115,3654988,3654136,3654673,3654786,3654115,3654988,3654136,3654673,3654115,3654988,3654144,3654673,3654988,3654144,3654673,3654988,3654144,3654673,3654988,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654673,3654673,3654673,3654673</t>
+          <t>3654136,3654019,3654242,3654019,3654668,3654253,3654136,3654019,3654242,3654019,3654668,3654253,3654136,3654019,3654242,3654019,3654668,3654325,3654136,3654019,3654242,3654019,3654668,3654325,3654136,3654091,3654242,3654091,3654668,3654541,3654136,3654091,3654466,3654091,3654668,3654565,3654136,3654091,3654466,3654091,3654668,3654645,3654136,3654099,3654466,3654099,3654868,3654645,3654136,3654099,3654466,3654099,3654868,3654693,3654136,3654099,3654514,3654099,3654868,3654693,3654136,3654099,3654514,3654099,3654868,3654709,3654136,3654107,3654514,3654107,3654868,3654709,3654136,3654107,3654514,3654107,3654868,3655021,3654136,3654107,3654786,3654107,3654868,3655021,3654136,3654107,3654786,3654107,3654988,3654136,3654115,3654786,3654115,3654988,3654136,3654115,3654786,3654115,3654988,3654136,3654115,3654115,3654988,3654144,3654673,3654988,3654144,3654673,3654988,3654144,3654673,3654988,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654144,3654673,3654673,3654673,3654673,3654673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L14 W18/25; N=146; EHP=9974.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x3,normal:17x18,normal:18x18,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L14 W18/25; N=146; EHP=23822.532028; air:2x8,air:11x6,air:12x8,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3656136,3656673,3656242,3656019,3656668,3656253,3656136,3656673,3656242,3656019,3656668,3656253,3656136,3656673,3656242,3656019,3656668,3656325,3656136,3656673,3656242,3656019,3656668,3656325,3656136,3656673,3656466,3656091,3656668,3656541,3656136,3656673,3656466,3656091,3656668,3656541,3656136,3656673,3656466,3656091,3656668,3656565,3656136,3656673,3656466,3656091,3656668,3656565,3656136,3656673,3656466,3656099,3656868,3656645,3656136,3656673,3656514,3656099,3656868,3656645,3656136,3656673,3656514,3656099,3656868,3656693,3656136,3656673,3656514,3656107,3656868,3656693,3656136,3656673,3656514,3656107,3656868,3656709,3656136,3656673,3656786,3656107,3656868,3657021,3656136,3656673,3656786,3656107,3656868,3657021,3656136,3656673,3656786,3656115,3656988,3656136,3656673,3656786,3656115,3656988,3656136,3656673,3656786,3656115,3656988,3656136,3656673,3656988,3656144,3656673,3656988,3656144,3656673,3656988,3656144,3656673,3656988,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656673,3656673,3656673,3656673,3656673</t>
+          <t>3656136,3656019,3656242,3656019,3656668,3656253,3656136,3656019,3656242,3656019,3656668,3656253,3656136,3656019,3656242,3656019,3656668,3656325,3656136,3656019,3656242,3656019,3656668,3656325,3656136,3656091,3656466,3656091,3656668,3656541,3656136,3656091,3656466,3656091,3656668,3656541,3656136,3656091,3656466,3656091,3656668,3656565,3656136,3656091,3656466,3656091,3656668,3656565,3656136,3656099,3656466,3656099,3656868,3656645,3656136,3656099,3656514,3656099,3656868,3656645,3656136,3656099,3656514,3656099,3656868,3656693,3656136,3656107,3656514,3656107,3656868,3656693,3656136,3656107,3656514,3656107,3656868,3656709,3656136,3656107,3656786,3656107,3656868,3657021,3656136,3656107,3656786,3656107,3656868,3657021,3656136,3656115,3656786,3656115,3656988,3656136,3656115,3656786,3656115,3656988,3656136,3656115,3656786,3656115,3656988,3656136,3656673,3656988,3656144,3656673,3656988,3656144,3656673,3656988,3656144,3656673,3656988,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656144,3656673,3656673,3656673,3656673,3656673,3656673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L14 W19/25; N=152; EHP=11552.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x19,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x42,heavy:86x2,heavy:88x1,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L14 W19/25; N=152; EHP=27577.037914; air:2x8,air:11x8,air:12x6,air:13x8,air:14x6,fast:30x4,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x8,medium:108x7,medium:123x7,normal:17x19,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3658136,3658673,3658242,3658019,3658668,3658253,3658542,3658136,3658673,3658242,3658019,3658668,3658253,3658136,3658673,3658242,3658019,3658668,3658325,3658136,3658673,3658242,3658091,3658668,3658325,3658136,3658673,3658466,3658091,3658668,3658541,3658136,3658673,3658466,3658091,3658668,3658541,3658136,3658673,3658466,3658091,3658668,3658565,3658136,3658673,3658466,3658099,3658868,3658565,3658136,3658673,3658466,3658099,3658868,3658645,3658136,3658673,3658514,3658099,3658868,3658693,3658136,3658673,3658514,3658099,3658868,3658693,3658136,3658673,3658514,3658107,3658868,3658709,3658136,3658673,3658514,3658107,3658868,3658709,3658136,3658673,3658514,3658107,3658868,3659021,3658136,3658673,3658786,3658107,3658868,3659021,3658136,3658673,3658786,3658115,3658988,3658136,3658673,3658786,3658115,3658988,3658136,3658673,3658786,3658115,3658988,3658136,3658673,3658115,3658988,3658144,3658673,3658988,3658144,3658673,3658988,3658144,3658673,3658988,3658144,3658673,3658988,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658673,3658673,3658673,3658673,3658673,3658673</t>
+          <t>3658136,3658019,3658242,3658019,3658668,3658253,3658542,3658136,3658019,3658242,3658019,3658668,3658253,3658136,3658019,3658242,3658019,3658668,3658325,3658136,3658091,3658242,3658091,3658668,3658325,3658136,3658091,3658466,3658091,3658668,3658541,3658136,3658091,3658466,3658091,3658668,3658541,3658136,3658091,3658466,3658091,3658668,3658565,3658136,3658099,3658466,3658099,3658868,3658565,3658136,3658099,3658466,3658099,3658868,3658645,3658136,3658099,3658514,3658099,3658868,3658693,3658136,3658099,3658514,3658099,3658868,3658693,3658136,3658107,3658514,3658107,3658868,3658709,3658136,3658107,3658514,3658107,3658868,3658709,3658136,3658107,3658514,3658107,3658868,3659021,3658136,3658107,3658786,3658107,3658868,3659021,3658136,3658115,3658786,3658115,3658988,3658136,3658115,3658786,3658115,3658988,3658136,3658115,3658786,3658115,3658988,3658136,3658115,3658115,3658988,3658144,3658673,3658988,3658144,3658673,3658988,3658144,3658673,3658988,3658144,3658673,3658988,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658144,3658673,3658673,3658673,3658673,3658673,3658673,3658673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L14 W20/25; N=158; EHP=19397.000000; air:2x3,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x44,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L14 W20/25; N=158; EHP=46303.238661; air:2x6,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x4,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017806,10017817,10017808,10048600,10017816,10017809,10017806,10017817,10017808,10048600,10017816,10017809,10017806,10017817,10017808,10048600,10017816,10017810,10017806,10017817,10017808,10048600,10017816,10017810,10017806,10017817,10017808,10017803,10017816,10017813,10017806,10017817,10017811,10017803,10017816,10017813,10017806,10017817,10017811,10017803,10017816,10017814,10017806,10017817,10017811,10017803,10017816,10017814,10017806,10017817,10017811,10048601,10017820,10017815,10017806,10017817,10017812,10048601,10017820,10017815,10017806,10017817,10017812,10048601,10017820,10045181,10017806,10017817,10017812,10048601,10017820,10045181,10017806,10017817,10017812,10017804,10017820,10017818,10017806,10017817,10017812,10017804,10017820,10017818,10017806,10017817,10017819,10017804,10017820,10017822,10017806,10017817,10017819,10017804,10017820,10017822,10017806,10017817,10017819,10017805,10017821,10017806,10017817,10017819,10017805,10017821,10017806,10017817,10017819,10017805,10017821,10017806,10017817,10017805,10017821,10017807,10017817,10017821,10017807,10017817,10017821,10017807,10017817,10017821,10017807,10017817,10017821,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017817,10017817,10017817,10017817,10017817</t>
+          <t>10017806,10048600,10017808,10048600,10017816,10017809,10017806,10048600,10017808,10048600,10017816,10017809,10017806,10048600,10017808,10048600,10017816,10017810,10017806,10048600,10017808,10048600,10017816,10017810,10017806,10017803,10017808,10017803,10017816,10017813,10017806,10017803,10017811,10017803,10017816,10017813,10017806,10017803,10017811,10017803,10017816,10017814,10017806,10017803,10017811,10017803,10017816,10017814,10017806,10048601,10017811,10048601,10017820,10017815,10017806,10048601,10017812,10048601,10017820,10017815,10017806,10048601,10017812,10048601,10017820,10045181,10017806,10048601,10017812,10048601,10017820,10045181,10017806,10017804,10017812,10017804,10017820,10017818,10017806,10017804,10017812,10017804,10017820,10017818,10017806,10017804,10017819,10017804,10017820,10017822,10017806,10017804,10017819,10017804,10017820,10017822,10017806,10017805,10017819,10017805,10017821,10017806,10017805,10017819,10017805,10017821,10017806,10017805,10017819,10017805,10017821,10017806,10017805,10017805,10017821,10017807,10017817,10017821,10017807,10017817,10017821,10017807,10017817,10017821,10017807,10017817,10017821,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017807,10017817,10017817,10017817,10017817,10017817,10017817</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L14 W21/25; N=164; EHP=19785.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L14 W21/25; N=164; EHP=47247.362285; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x4,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017826,10017836,10017828,10048602,10017835,10045182,10017826,10017836,10017828,10048602,10017835,10045182,10017826,10017836,10017828,10048602,10017835,10017829,10017826,10017836,10017828,10048602,10017835,10017829,10017826,10017836,10017828,10017823,10017835,10017829,10017826,10017836,10017830,10017823,10017835,10017832,10017826,10017836,10017830,10017823,10017835,10017832,10017826,10017836,10017830,10017823,10017835,10017833,10017826,10017836,10017830,10048603,10017835,10017833,10017826,10017836,10017830,10048603,10017840,10017834,10017826,10017836,10017831,10048603,10017840,10017834,10017826,10017836,10017831,10048603,10017840,10017837,10017826,10017836,10017831,10017824,10017840,10017837,10017826,10017836,10017831,10017824,10017840,10017838,10017826,10017836,10017831,10017824,10017840,10017838,10017826,10017836,10017839,10017824,10017840,10017842,10017826,10017836,10017839,10017825,10017840,10017842,10017826,10017836,10017839,10017825,10017841,10017826,10017836,10017839,10017825,10017841,10017826,10017836,10017839,10017825,10017841,10017827,10017836,10017841,10017827,10017836,10017841,10017827,10017836,10017841,10017827,10017836,10017841,10017827,10017836,10017841,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017836,10017836,10017836,10017836,10017836,10017836</t>
+          <t>10017826,10048602,10017828,10048602,10017835,10045182,10017826,10048602,10017828,10048602,10017835,10045182,10017826,10048602,10017828,10048602,10017835,10017829,10017826,10048602,10017828,10048602,10017835,10017829,10017826,10017823,10017828,10017823,10017835,10017829,10017826,10017823,10017830,10017823,10017835,10017832,10017826,10017823,10017830,10017823,10017835,10017832,10017826,10017823,10017830,10017823,10017835,10017833,10017826,10048603,10017830,10048603,10017835,10017833,10017826,10048603,10017830,10048603,10017840,10017834,10017826,10048603,10017831,10048603,10017840,10017834,10017826,10048603,10017831,10048603,10017840,10017837,10017826,10017824,10017831,10017824,10017840,10017837,10017826,10017824,10017831,10017824,10017840,10017838,10017826,10017824,10017831,10017824,10017840,10017838,10017826,10017824,10017839,10017824,10017840,10017842,10017826,10017825,10017839,10017825,10017840,10017842,10017826,10017825,10017839,10017825,10017841,10017826,10017825,10017839,10017825,10017841,10017826,10017825,10017839,10017825,10017841,10017827,10017836,10017841,10017827,10017836,10017841,10017827,10017836,10017841,10017827,10017836,10017841,10017827,10017836,10017841,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017827,10017836,10017836,10017836,10017836,10017836,10017836,10017836</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L14 W22/25; N=170; EHP=20181.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x5,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L14 W22/25; N=170; EHP=48170.813821; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x8,normal:17x20,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017846,10017856,10017848,10048604,10017855,10017849,10017846,10017856,10017848,10048604,10017855,10017849,10017846,10017856,10017848,10048604,10017855,10045183,10017846,10017856,10017848,10048604,10017855,10045183,10017846,10017856,10017848,10017843,10017855,10017852,10017846,10017856,10017850,10017843,10017855,10017852,10017846,10017856,10017850,10017843,10017855,10017853,10017846,10017856,10017850,10017843,10017855,10017853,10017846,10017856,10017850,10048605,10017860,10017854,10017846,10017856,10017850,10048605,10017860,10017854,10017846,10017856,10017851,10048605,10017860,10017857,10017846,10017856,10017851,10048605,10017860,10017857,10017846,10017856,10017851,10048605,10017860,10017858,10017846,10017856,10017851,10017844,10017860,10017858,10017846,10017856,10017851,10017844,10017860,10017862,10017846,10017856,10017859,10017844,10017860,10017862,10017846,10017856,10017859,10017844,10017860,10017862,10017846,10017856,10017859,10017845,10017861,10017846,10017856,10017859,10017845,10017861,10017846,10017856,10017859,10017845,10017861,10017846,10017856,10017859,10017845,10017861,10017847,10017856,10017861,10017847,10017856,10017861,10017847,10017856,10017861,10017847,10017856,10017861,10017847,10017856,10017861,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017856,10017856,10017856,10017856,10017856,10017856,10017856</t>
+          <t>10017846,10048604,10017848,10048604,10017855,10017849,10017846,10048604,10017848,10048604,10017855,10017849,10017846,10048604,10017848,10048604,10017855,10045183,10017846,10048604,10017848,10048604,10017855,10045183,10017846,10017843,10017848,10017843,10017855,10017852,10017846,10017843,10017850,10017843,10017855,10017852,10017846,10017843,10017850,10017843,10017855,10017853,10017846,10017843,10017850,10017843,10017855,10017853,10017846,10048605,10017850,10048605,10017860,10017854,10017846,10048605,10017850,10048605,10017860,10017854,10017846,10048605,10017851,10048605,10017860,10017857,10017846,10048605,10017851,10048605,10017860,10017857,10017846,10048605,10017851,10048605,10017860,10017858,10017846,10017844,10017851,10017844,10017860,10017858,10017846,10017844,10017851,10017844,10017860,10017862,10017846,10017844,10017859,10017844,10017860,10017862,10017846,10017844,10017859,10017844,10017860,10017862,10017846,10017845,10017859,10017845,10017861,10017846,10017845,10017859,10017845,10017861,10017846,10017845,10017859,10017845,10017861,10017846,10017845,10017859,10017845,10017861,10017847,10017856,10017861,10017847,10017856,10017861,10017847,10017856,10017861,10017847,10017856,10017861,10017847,10017856,10017861,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017847,10017856,10017856,10017856,10017856,10017856,10017856,10017856,10017856</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L14 W23/25; N=176; EHP=20585.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x3</t>
+          <t>L14 W23/25; N=176; EHP=49145.842303; air:2x8,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x8,medium:108x9,medium:123x9,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017866,10017877,10017868,10048606,10017876,10017869,10017866,10017877,10017868,10048606,10017876,10017869,10017866,10017877,10017868,10048606,10017876,10017870,10017866,10017877,10017868,10048606,10017876,10017870,10017866,10017877,10017868,10048606,10017876,10017873,10017866,10017877,10017871,10017863,10017876,10017873,10017866,10017877,10017871,10017863,10017876,10017873,10017866,10017877,10017871,10017863,10017876,10017874,10017866,10017877,10017871,10017863,10017876,10017874,10017866,10017877,10017871,10048607,10017881,10017874,10017866,10017877,10017871,10048607,10017881,10017875,10017866,10017877,10017872,10048607,10017881,10017875,10017866,10017877,10017872,10048607,10017881,10017878,10017866,10017877,10017872,10017864,10017881,10017878,10017866,10017877,10017872,10017864,10017881,10017879,10017866,10017877,10017872,10017864,10017881,10017879,10017866,10017877,10017880,10017864,10017881,10045184,10017866,10017877,10017880,10017864,10017881,10045184,10017866,10017877,10017880,10017865,10017882,10017866,10017877,10017880,10017865,10017882,10017866,10017877,10017880,10017865,10017882,10017866,10017877,10017865,10017882,10017867,10017877,10017882,10017867,10017877,10017882,10017867,10017877,10017882,10017867,10017877,10017882,10017867,10017877,10017882,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017877,10017877,10017877,10017877,10017877,10017877</t>
+          <t>10017866,10048606,10017868,10048606,10017876,10017869,10017866,10048606,10017868,10048606,10017876,10017869,10017866,10048606,10017868,10048606,10017876,10017870,10017866,10048606,10017868,10048606,10017876,10017870,10017866,10048606,10017868,10048606,10017876,10017873,10017866,10017863,10017871,10017863,10017876,10017873,10017866,10017863,10017871,10017863,10017876,10017873,10017866,10017863,10017871,10017863,10017876,10017874,10017866,10017863,10017871,10017863,10017876,10017874,10017866,10048607,10017871,10048607,10017881,10017874,10017866,10048607,10017871,10048607,10017881,10017875,10017866,10048607,10017872,10048607,10017881,10017875,10017866,10048607,10017872,10048607,10017881,10017878,10017866,10017864,10017872,10017864,10017881,10017878,10017866,10017864,10017872,10017864,10017881,10017879,10017866,10017864,10017872,10017864,10017881,10017879,10017866,10017864,10017880,10017864,10017881,10045184,10017866,10017864,10017880,10017864,10017881,10045184,10017866,10017865,10017880,10017865,10017882,10017866,10017865,10017880,10017865,10017882,10017866,10017865,10017880,10017865,10017882,10017866,10017865,10017865,10017882,10017867,10017877,10017882,10017867,10017877,10017882,10017867,10017877,10017882,10017867,10017877,10017882,10017867,10017877,10017882,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017867,10017877,10017877,10017877,10017877,10017877,10017877,10017877</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L14 W24/25; N=182; EHP=22043.000000; air:2x5,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L14 W24/25; N=182; EHP=52632.121349; air:2x10,air:11x8,air:12x8,air:13x10,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017886,10017896,10017888,10048608,10017895,10017889,10017903,10017886,10017896,10017888,10048608,10017895,10017889,10017886,10017896,10017888,10048608,10017895,10017890,10017886,10017896,10017888,10048608,10017895,10017890,10017886,10017896,10017888,10017883,10017895,10017893,10017886,10017896,10017888,10017883,10017895,10017893,10017886,10017896,10017891,10017883,10017895,10017893,10017886,10017896,10017891,10017883,10017895,10045185,10017886,10017896,10017891,10017883,10017895,10045185,10017886,10017896,10017891,10048609,10017895,10017894,10017886,10017896,10017891,10048609,10017900,10017894,10017886,10017896,10017892,10048609,10017900,10017897,10017886,10017896,10017892,10048609,10017900,10017897,10017886,10017896,10017892,10017884,10017900,10017898,10017886,10017896,10017892,10017884,10017900,10017898,10017886,10017896,10017892,10017884,10017900,10017898,10017886,10017896,10017892,10017884,10017900,10017902,10017886,10017896,10017899,10017884,10017900,10017902,10017886,10017896,10017899,10017885,10017900,10017886,10017896,10017899,10017885,10017901,10017886,10017896,10017899,10017885,10017901,10017886,10017896,10017899,10017885,10017901,10017887,10017896,10017885,10017901,10017887,10017896,10017901,10017887,10017896,10017901,10017887,10017896,10017901,10017887,10017896,10017901,10017887,10017896,10017901,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017896,10017896,10017896,10017896,10017896,10017896,10017896,10017896</t>
+          <t>10017886,10048608,10017888,10048608,10017895,10017889,10017903,10017886,10048608,10017888,10048608,10017895,10017889,10017886,10048608,10017888,10048608,10017895,10017890,10017886,10048608,10017888,10048608,10017895,10017890,10017886,10017883,10017888,10017883,10017895,10017893,10017886,10017883,10017888,10017883,10017895,10017893,10017886,10017883,10017891,10017883,10017895,10017893,10017886,10017883,10017891,10017883,10017895,10045185,10017886,10017883,10017891,10017883,10017895,10045185,10017886,10048609,10017891,10048609,10017895,10017894,10017886,10048609,10017891,10048609,10017900,10017894,10017886,10048609,10017892,10048609,10017900,10017897,10017886,10048609,10017892,10048609,10017900,10017897,10017886,10017884,10017892,10017884,10017900,10017898,10017886,10017884,10017892,10017884,10017900,10017898,10017886,10017884,10017892,10017884,10017900,10017898,10017886,10017884,10017892,10017884,10017900,10017902,10017886,10017884,10017899,10017884,10017900,10017902,10017886,10017885,10017899,10017885,10017900,10017886,10017885,10017899,10017885,10017901,10017886,10017885,10017899,10017885,10017901,10017886,10017885,10017899,10017885,10017901,10017887,10017885,10017885,10017901,10017887,10017896,10017901,10017887,10017896,10017901,10017887,10017896,10017901,10017887,10017896,10017901,10017887,10017896,10017901,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017887,10017896,10017896,10017896,10017896,10017896,10017896,10017896,10017896,10017896</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L14 W25/25; N=188; EHP=43997.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x22,normal:18x22,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x6,heavy:67x3,heavy:70x2,heavy:80x2,medium:83x10,swarm:84x52,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x9,heavy:127x2,boss:131x1</t>
+          <t>L14 W25/25; N=188; EHP=105047.654195; air:2x8,air:11x10,air:12x8,air:13x10,air:14x10,boss:131x1,fast:30x6,fast:58x5,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x10,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L14/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L14/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>254</v>
+        <v>320</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>233</v>
+        <v>350</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>219</v>
+        <v>300</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>191</v>
+        <v>350</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>184</v>
+        <v>270</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>163</v>
+        <v>260</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>149</v>
+        <v>350</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>142</v>
+        <v>270</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>350</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
